--- a/TAP n NRT directories.xlsx
+++ b/TAP n NRT directories.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="29" documentId="8_{75BF60A8-BB22-4744-A2CE-ACD735186B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03656DF8-AD99-4364-AC52-876415F14205}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0E8EA9B8-1E59-4C3E-9E23-98E6D03B5A03}"/>
+    <workbookView minimized="1" xWindow="4800" yWindow="3110" windowWidth="14400" windowHeight="8170" xr2:uid="{0E8EA9B8-1E59-4C3E-9E23-98E6D03B5A03}"/>
   </bookViews>
   <sheets>
     <sheet name="TAP" sheetId="1" r:id="rId1"/>
@@ -7768,7 +7768,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8163,16 +8163,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C179C80-64E6-4AB7-A6DA-DF002A5DD816}">
   <dimension ref="A1:F627"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.42578125" customWidth="1"/>
-    <col min="6" max="6" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.453125" customWidth="1"/>
+    <col min="6" max="6" width="37.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8192,7 +8192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -8212,7 +8212,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -8232,7 +8232,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -8252,7 +8252,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
@@ -8272,7 +8272,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
@@ -8312,7 +8312,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -8324,7 +8324,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>33</v>
       </c>
@@ -8342,7 +8342,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
@@ -8362,7 +8362,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>40</v>
       </c>
@@ -8382,7 +8382,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
@@ -8402,7 +8402,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>48</v>
       </c>
@@ -8422,7 +8422,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>52</v>
       </c>
@@ -8442,7 +8442,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>56</v>
       </c>
@@ -8462,7 +8462,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>60</v>
       </c>
@@ -8482,7 +8482,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>64</v>
       </c>
@@ -8502,7 +8502,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>68</v>
       </c>
@@ -8522,7 +8522,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>72</v>
       </c>
@@ -8542,7 +8542,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>76</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>80</v>
       </c>
@@ -8582,7 +8582,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>84</v>
       </c>
@@ -8602,7 +8602,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>88</v>
       </c>
@@ -8622,7 +8622,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>92</v>
       </c>
@@ -8642,7 +8642,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>96</v>
       </c>
@@ -8662,7 +8662,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>100</v>
       </c>
@@ -8682,7 +8682,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>104</v>
       </c>
@@ -8702,7 +8702,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>108</v>
       </c>
@@ -8722,7 +8722,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>112</v>
       </c>
@@ -8742,7 +8742,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>116</v>
       </c>
@@ -8762,7 +8762,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>120</v>
       </c>
@@ -8782,7 +8782,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>124</v>
       </c>
@@ -8802,7 +8802,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>128</v>
       </c>
@@ -8822,7 +8822,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>132</v>
       </c>
@@ -8842,7 +8842,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>136</v>
       </c>
@@ -8862,7 +8862,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>140</v>
       </c>
@@ -8882,7 +8882,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>144</v>
       </c>
@@ -8902,7 +8902,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>148</v>
       </c>
@@ -8922,7 +8922,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>152</v>
       </c>
@@ -8942,7 +8942,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>156</v>
       </c>
@@ -8962,7 +8962,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>160</v>
       </c>
@@ -8982,7 +8982,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>164</v>
       </c>
@@ -9002,7 +9002,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>168</v>
       </c>
@@ -9022,7 +9022,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>172</v>
       </c>
@@ -9042,7 +9042,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>176</v>
       </c>
@@ -9062,7 +9062,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>180</v>
       </c>
@@ -9082,7 +9082,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>184</v>
       </c>
@@ -9102,7 +9102,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>188</v>
       </c>
@@ -9122,7 +9122,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>192</v>
       </c>
@@ -9142,7 +9142,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>196</v>
       </c>
@@ -9162,7 +9162,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>200</v>
       </c>
@@ -9182,7 +9182,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>204</v>
       </c>
@@ -9202,7 +9202,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>208</v>
       </c>
@@ -9222,7 +9222,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>212</v>
       </c>
@@ -9242,7 +9242,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>216</v>
       </c>
@@ -9262,7 +9262,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>220</v>
       </c>
@@ -9282,7 +9282,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>224</v>
       </c>
@@ -9302,7 +9302,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>228</v>
       </c>
@@ -9322,7 +9322,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>232</v>
       </c>
@@ -9342,7 +9342,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>236</v>
       </c>
@@ -9362,7 +9362,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>240</v>
       </c>
@@ -9382,7 +9382,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>244</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>248</v>
       </c>
@@ -9422,7 +9422,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>252</v>
       </c>
@@ -9442,7 +9442,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>256</v>
       </c>
@@ -9462,7 +9462,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>260</v>
       </c>
@@ -9482,7 +9482,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>264</v>
       </c>
@@ -9502,7 +9502,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>268</v>
       </c>
@@ -9522,7 +9522,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>272</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>276</v>
       </c>
@@ -9562,7 +9562,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>280</v>
       </c>
@@ -9582,7 +9582,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>284</v>
       </c>
@@ -9602,7 +9602,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>288</v>
       </c>
@@ -9622,7 +9622,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>292</v>
       </c>
@@ -9642,7 +9642,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>296</v>
       </c>
@@ -9662,7 +9662,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>300</v>
       </c>
@@ -9682,7 +9682,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>304</v>
       </c>
@@ -9702,7 +9702,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>308</v>
       </c>
@@ -9722,7 +9722,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>312</v>
       </c>
@@ -9742,7 +9742,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>316</v>
       </c>
@@ -9762,7 +9762,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>320</v>
       </c>
@@ -9782,7 +9782,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>324</v>
       </c>
@@ -9802,7 +9802,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>328</v>
       </c>
@@ -9822,7 +9822,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>332</v>
       </c>
@@ -9842,7 +9842,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>336</v>
       </c>
@@ -9862,7 +9862,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>340</v>
       </c>
@@ -9882,7 +9882,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>344</v>
       </c>
@@ -9902,7 +9902,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>348</v>
       </c>
@@ -9922,7 +9922,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>352</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>356</v>
       </c>
@@ -9962,7 +9962,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>360</v>
       </c>
@@ -9982,7 +9982,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>364</v>
       </c>
@@ -10002,7 +10002,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>368</v>
       </c>
@@ -10022,7 +10022,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>372</v>
       </c>
@@ -10042,7 +10042,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>376</v>
       </c>
@@ -10062,7 +10062,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>380</v>
       </c>
@@ -10082,7 +10082,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>384</v>
       </c>
@@ -10102,7 +10102,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>388</v>
       </c>
@@ -10122,7 +10122,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>392</v>
       </c>
@@ -10142,7 +10142,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>396</v>
       </c>
@@ -10162,7 +10162,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>400</v>
       </c>
@@ -10182,7 +10182,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>404</v>
       </c>
@@ -10202,7 +10202,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>408</v>
       </c>
@@ -10222,7 +10222,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>412</v>
       </c>
@@ -10242,7 +10242,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>416</v>
       </c>
@@ -10262,7 +10262,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>420</v>
       </c>
@@ -10282,7 +10282,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>424</v>
       </c>
@@ -10302,7 +10302,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>428</v>
       </c>
@@ -10322,7 +10322,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>432</v>
       </c>
@@ -10342,7 +10342,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>436</v>
       </c>
@@ -10362,7 +10362,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>440</v>
       </c>
@@ -10382,7 +10382,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>444</v>
       </c>
@@ -10402,7 +10402,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>448</v>
       </c>
@@ -10422,7 +10422,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>452</v>
       </c>
@@ -10442,7 +10442,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>456</v>
       </c>
@@ -10462,7 +10462,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>460</v>
       </c>
@@ -10482,7 +10482,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>464</v>
       </c>
@@ -10502,7 +10502,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>468</v>
       </c>
@@ -10522,7 +10522,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>472</v>
       </c>
@@ -10542,7 +10542,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>476</v>
       </c>
@@ -10562,7 +10562,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>480</v>
       </c>
@@ -10582,7 +10582,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>484</v>
       </c>
@@ -10602,7 +10602,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>488</v>
       </c>
@@ -10622,7 +10622,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>492</v>
       </c>
@@ -10642,7 +10642,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>496</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>500</v>
       </c>
@@ -10682,7 +10682,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>504</v>
       </c>
@@ -10702,7 +10702,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>508</v>
       </c>
@@ -10722,7 +10722,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>512</v>
       </c>
@@ -10742,7 +10742,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>516</v>
       </c>
@@ -10762,7 +10762,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>520</v>
       </c>
@@ -10782,7 +10782,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>524</v>
       </c>
@@ -10802,7 +10802,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>528</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>532</v>
       </c>
@@ -10842,7 +10842,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>536</v>
       </c>
@@ -10862,7 +10862,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>540</v>
       </c>
@@ -10882,7 +10882,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>544</v>
       </c>
@@ -10902,7 +10902,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>548</v>
       </c>
@@ -10922,7 +10922,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>552</v>
       </c>
@@ -10942,7 +10942,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>556</v>
       </c>
@@ -10962,7 +10962,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>560</v>
       </c>
@@ -10982,7 +10982,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>564</v>
       </c>
@@ -11002,7 +11002,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>568</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>572</v>
       </c>
@@ -11042,7 +11042,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>576</v>
       </c>
@@ -11062,7 +11062,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>580</v>
       </c>
@@ -11082,7 +11082,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>584</v>
       </c>
@@ -11102,7 +11102,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>588</v>
       </c>
@@ -11122,7 +11122,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>592</v>
       </c>
@@ -11142,7 +11142,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>596</v>
       </c>
@@ -11162,7 +11162,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>600</v>
       </c>
@@ -11182,7 +11182,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>604</v>
       </c>
@@ -11202,7 +11202,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>608</v>
       </c>
@@ -11222,7 +11222,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>612</v>
       </c>
@@ -11242,7 +11242,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>616</v>
       </c>
@@ -11262,7 +11262,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>620</v>
       </c>
@@ -11282,7 +11282,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>624</v>
       </c>
@@ -11302,7 +11302,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>628</v>
       </c>
@@ -11322,7 +11322,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>632</v>
       </c>
@@ -11342,7 +11342,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>636</v>
       </c>
@@ -11362,7 +11362,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>640</v>
       </c>
@@ -11382,7 +11382,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>644</v>
       </c>
@@ -11402,7 +11402,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>648</v>
       </c>
@@ -11422,7 +11422,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>652</v>
       </c>
@@ -11442,7 +11442,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>656</v>
       </c>
@@ -11462,7 +11462,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>660</v>
       </c>
@@ -11482,7 +11482,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>664</v>
       </c>
@@ -11502,7 +11502,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>668</v>
       </c>
@@ -11522,7 +11522,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>672</v>
       </c>
@@ -11542,7 +11542,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>676</v>
       </c>
@@ -11562,7 +11562,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>680</v>
       </c>
@@ -11582,7 +11582,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>684</v>
       </c>
@@ -11602,7 +11602,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>688</v>
       </c>
@@ -11622,7 +11622,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>692</v>
       </c>
@@ -11642,7 +11642,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>696</v>
       </c>
@@ -11662,7 +11662,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>700</v>
       </c>
@@ -11682,7 +11682,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>704</v>
       </c>
@@ -11702,7 +11702,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>708</v>
       </c>
@@ -11722,7 +11722,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>712</v>
       </c>
@@ -11742,7 +11742,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>716</v>
       </c>
@@ -11762,7 +11762,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>720</v>
       </c>
@@ -11782,7 +11782,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>724</v>
       </c>
@@ -11802,7 +11802,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>728</v>
       </c>
@@ -11822,7 +11822,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>732</v>
       </c>
@@ -11842,7 +11842,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>736</v>
       </c>
@@ -11862,7 +11862,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
         <v>740</v>
       </c>
@@ -11882,7 +11882,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
         <v>744</v>
       </c>
@@ -11902,7 +11902,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>748</v>
       </c>
@@ -11922,7 +11922,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>752</v>
       </c>
@@ -11942,7 +11942,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>756</v>
       </c>
@@ -11962,7 +11962,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>760</v>
       </c>
@@ -11982,7 +11982,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="192" spans="1:6">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>764</v>
       </c>
@@ -12002,7 +12002,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="193" spans="1:6">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>768</v>
       </c>
@@ -12022,7 +12022,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="194" spans="1:6">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>772</v>
       </c>
@@ -12042,7 +12042,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="195" spans="1:6">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>776</v>
       </c>
@@ -12062,7 +12062,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="196" spans="1:6">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>780</v>
       </c>
@@ -12082,7 +12082,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="197" spans="1:6">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>784</v>
       </c>
@@ -12102,7 +12102,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="198" spans="1:6">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>788</v>
       </c>
@@ -12122,7 +12122,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="199" spans="1:6">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>792</v>
       </c>
@@ -12142,7 +12142,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="200" spans="1:6">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>796</v>
       </c>
@@ -12162,7 +12162,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="201" spans="1:6">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>800</v>
       </c>
@@ -12182,7 +12182,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="202" spans="1:6">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>804</v>
       </c>
@@ -12202,7 +12202,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="203" spans="1:6">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
         <v>808</v>
       </c>
@@ -12222,7 +12222,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="204" spans="1:6">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>812</v>
       </c>
@@ -12242,7 +12242,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="205" spans="1:6">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>816</v>
       </c>
@@ -12262,7 +12262,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="206" spans="1:6">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>820</v>
       </c>
@@ -12282,7 +12282,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="207" spans="1:6">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>824</v>
       </c>
@@ -12302,7 +12302,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="208" spans="1:6">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
         <v>828</v>
       </c>
@@ -12322,7 +12322,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="209" spans="1:6">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>832</v>
       </c>
@@ -12342,7 +12342,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="210" spans="1:6">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>836</v>
       </c>
@@ -12362,7 +12362,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="211" spans="1:6">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
         <v>840</v>
       </c>
@@ -12382,7 +12382,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="212" spans="1:6">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>844</v>
       </c>
@@ -12402,7 +12402,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="213" spans="1:6">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>848</v>
       </c>
@@ -12422,7 +12422,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="214" spans="1:6">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>852</v>
       </c>
@@ -12442,7 +12442,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="215" spans="1:6">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
         <v>856</v>
       </c>
@@ -12462,7 +12462,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="216" spans="1:6">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
         <v>860</v>
       </c>
@@ -12482,7 +12482,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="217" spans="1:6">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>864</v>
       </c>
@@ -12502,7 +12502,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="218" spans="1:6">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
         <v>868</v>
       </c>
@@ -12522,7 +12522,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="219" spans="1:6">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>872</v>
       </c>
@@ -12542,7 +12542,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="220" spans="1:6">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>876</v>
       </c>
@@ -12562,7 +12562,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="221" spans="1:6">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>880</v>
       </c>
@@ -12582,7 +12582,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="222" spans="1:6">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
         <v>884</v>
       </c>
@@ -12602,7 +12602,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="223" spans="1:6">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
         <v>888</v>
       </c>
@@ -12622,7 +12622,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="224" spans="1:6">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
         <v>892</v>
       </c>
@@ -12642,7 +12642,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="225" spans="1:6">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>896</v>
       </c>
@@ -12662,7 +12662,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="226" spans="1:6">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>900</v>
       </c>
@@ -12682,7 +12682,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="227" spans="1:6">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>904</v>
       </c>
@@ -12702,7 +12702,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="228" spans="1:6">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>908</v>
       </c>
@@ -12722,7 +12722,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="229" spans="1:6">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>912</v>
       </c>
@@ -12742,7 +12742,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="230" spans="1:6">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>916</v>
       </c>
@@ -12762,7 +12762,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="231" spans="1:6">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>920</v>
       </c>
@@ -12782,7 +12782,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="232" spans="1:6">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>924</v>
       </c>
@@ -12802,7 +12802,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="233" spans="1:6">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>928</v>
       </c>
@@ -12822,7 +12822,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="234" spans="1:6">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>932</v>
       </c>
@@ -12842,7 +12842,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="235" spans="1:6">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>936</v>
       </c>
@@ -12862,7 +12862,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="236" spans="1:6">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>940</v>
       </c>
@@ -12882,7 +12882,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="237" spans="1:6">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
         <v>944</v>
       </c>
@@ -12902,7 +12902,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="238" spans="1:6">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
         <v>948</v>
       </c>
@@ -12922,7 +12922,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="239" spans="1:6">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
         <v>952</v>
       </c>
@@ -12942,7 +12942,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="240" spans="1:6">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
         <v>956</v>
       </c>
@@ -12962,7 +12962,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="241" spans="1:6">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
         <v>960</v>
       </c>
@@ -12982,7 +12982,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="242" spans="1:6">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
         <v>964</v>
       </c>
@@ -13002,7 +13002,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="243" spans="1:6">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" s="1" t="s">
         <v>968</v>
       </c>
@@ -13022,7 +13022,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="244" spans="1:6">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
         <v>972</v>
       </c>
@@ -13042,7 +13042,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="245" spans="1:6">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" s="1" t="s">
         <v>976</v>
       </c>
@@ -13062,7 +13062,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="246" spans="1:6">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
         <v>980</v>
       </c>
@@ -13082,7 +13082,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="247" spans="1:6">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" s="1" t="s">
         <v>984</v>
       </c>
@@ -13102,7 +13102,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="248" spans="1:6">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
         <v>988</v>
       </c>
@@ -13122,7 +13122,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="249" spans="1:6">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A249" s="1" t="s">
         <v>992</v>
       </c>
@@ -13142,7 +13142,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="250" spans="1:6">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A250" s="1" t="s">
         <v>996</v>
       </c>
@@ -13162,7 +13162,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="251" spans="1:6">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A251" s="1" t="s">
         <v>1000</v>
       </c>
@@ -13182,7 +13182,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="252" spans="1:6">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A252" s="1" t="s">
         <v>1004</v>
       </c>
@@ -13202,7 +13202,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="253" spans="1:6">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A253" s="1" t="s">
         <v>1008</v>
       </c>
@@ -13222,7 +13222,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="254" spans="1:6">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A254" s="1" t="s">
         <v>1012</v>
       </c>
@@ -13242,7 +13242,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="255" spans="1:6">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A255" s="1" t="s">
         <v>1016</v>
       </c>
@@ -13262,7 +13262,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="256" spans="1:6">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A256" s="1" t="s">
         <v>1020</v>
       </c>
@@ -13282,7 +13282,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="257" spans="1:6">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A257" s="1" t="s">
         <v>1024</v>
       </c>
@@ -13302,7 +13302,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="258" spans="1:6">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A258" s="1" t="s">
         <v>1028</v>
       </c>
@@ -13322,7 +13322,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="259" spans="1:6">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
         <v>1032</v>
       </c>
@@ -13342,7 +13342,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="260" spans="1:6">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
         <v>1036</v>
       </c>
@@ -13362,7 +13362,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="261" spans="1:6">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
         <v>1040</v>
       </c>
@@ -13382,7 +13382,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="262" spans="1:6">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
         <v>1044</v>
       </c>
@@ -13402,7 +13402,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="263" spans="1:6">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
         <v>1048</v>
       </c>
@@ -13422,7 +13422,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="264" spans="1:6">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
         <v>1052</v>
       </c>
@@ -13442,7 +13442,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="265" spans="1:6">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
         <v>1056</v>
       </c>
@@ -13462,7 +13462,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="266" spans="1:6">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
         <v>1060</v>
       </c>
@@ -13482,7 +13482,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="267" spans="1:6">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
         <v>1064</v>
       </c>
@@ -13502,7 +13502,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="268" spans="1:6">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A268" s="1" t="s">
         <v>1068</v>
       </c>
@@ -13522,7 +13522,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="269" spans="1:6">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
         <v>1072</v>
       </c>
@@ -13542,7 +13542,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="270" spans="1:6">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A270" s="1" t="s">
         <v>1076</v>
       </c>
@@ -13562,7 +13562,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="271" spans="1:6">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A271" s="1" t="s">
         <v>1080</v>
       </c>
@@ -13582,7 +13582,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="272" spans="1:6">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A272" s="1" t="s">
         <v>1084</v>
       </c>
@@ -13602,7 +13602,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="273" spans="1:6">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A273" s="1" t="s">
         <v>1088</v>
       </c>
@@ -13622,7 +13622,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="274" spans="1:6">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A274" s="1" t="s">
         <v>1092</v>
       </c>
@@ -13642,7 +13642,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="275" spans="1:6">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A275" s="1" t="s">
         <v>1096</v>
       </c>
@@ -13662,7 +13662,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="276" spans="1:6">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A276" s="1" t="s">
         <v>1100</v>
       </c>
@@ -13682,7 +13682,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="277" spans="1:6">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A277" s="1" t="s">
         <v>1104</v>
       </c>
@@ -13702,7 +13702,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="278" spans="1:6">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A278" s="1" t="s">
         <v>1108</v>
       </c>
@@ -13722,7 +13722,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="279" spans="1:6">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A279" s="1" t="s">
         <v>1112</v>
       </c>
@@ -13742,7 +13742,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="280" spans="1:6">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A280" s="1" t="s">
         <v>1116</v>
       </c>
@@ -13762,7 +13762,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="281" spans="1:6">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A281" s="1" t="s">
         <v>1120</v>
       </c>
@@ -13782,7 +13782,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="282" spans="1:6">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A282" s="1" t="s">
         <v>1124</v>
       </c>
@@ -13802,7 +13802,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="283" spans="1:6">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A283" s="1" t="s">
         <v>1128</v>
       </c>
@@ -13822,7 +13822,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="284" spans="1:6">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A284" s="1" t="s">
         <v>1132</v>
       </c>
@@ -13842,7 +13842,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="285" spans="1:6">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A285" s="1" t="s">
         <v>1136</v>
       </c>
@@ -13862,7 +13862,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="286" spans="1:6">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A286" s="1" t="s">
         <v>1140</v>
       </c>
@@ -13882,7 +13882,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="287" spans="1:6">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A287" s="1" t="s">
         <v>1144</v>
       </c>
@@ -13902,7 +13902,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="288" spans="1:6">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A288" s="1" t="s">
         <v>1148</v>
       </c>
@@ -13922,7 +13922,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="289" spans="1:6">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A289" s="1" t="s">
         <v>1152</v>
       </c>
@@ -13942,7 +13942,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="290" spans="1:6">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A290" s="1" t="s">
         <v>1156</v>
       </c>
@@ -13962,7 +13962,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="291" spans="1:6">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A291" s="1" t="s">
         <v>1160</v>
       </c>
@@ -13982,7 +13982,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="292" spans="1:6">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A292" s="1" t="s">
         <v>1164</v>
       </c>
@@ -14002,7 +14002,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="293" spans="1:6">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A293" s="1" t="s">
         <v>1168</v>
       </c>
@@ -14022,7 +14022,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="294" spans="1:6">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A294" s="1" t="s">
         <v>1172</v>
       </c>
@@ -14042,7 +14042,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="295" spans="1:6">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A295" s="1" t="s">
         <v>1176</v>
       </c>
@@ -14062,7 +14062,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="296" spans="1:6">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A296" s="1" t="s">
         <v>1180</v>
       </c>
@@ -14082,7 +14082,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="297" spans="1:6">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A297" s="1" t="s">
         <v>1184</v>
       </c>
@@ -14102,7 +14102,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="298" spans="1:6">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A298" s="1" t="s">
         <v>1188</v>
       </c>
@@ -14122,7 +14122,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="299" spans="1:6">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A299" s="1" t="s">
         <v>1192</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="300" spans="1:6">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A300" s="1" t="s">
         <v>1196</v>
       </c>
@@ -14162,7 +14162,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="301" spans="1:6">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A301" s="1" t="s">
         <v>1200</v>
       </c>
@@ -14182,7 +14182,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="302" spans="1:6">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A302" s="1" t="s">
         <v>1204</v>
       </c>
@@ -14202,7 +14202,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="303" spans="1:6">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A303" s="1" t="s">
         <v>1208</v>
       </c>
@@ -14222,7 +14222,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="304" spans="1:6">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A304" s="1" t="s">
         <v>1212</v>
       </c>
@@ -14242,7 +14242,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="305" spans="1:6">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A305" s="1" t="s">
         <v>1216</v>
       </c>
@@ -14262,7 +14262,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="306" spans="1:6">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A306" s="1" t="s">
         <v>1220</v>
       </c>
@@ -14282,7 +14282,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="307" spans="1:6">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A307" s="1" t="s">
         <v>1224</v>
       </c>
@@ -14302,7 +14302,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="308" spans="1:6">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A308" s="1" t="s">
         <v>1228</v>
       </c>
@@ -14322,7 +14322,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="309" spans="1:6">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A309" s="1" t="s">
         <v>1232</v>
       </c>
@@ -14342,7 +14342,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="310" spans="1:6">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A310" s="1" t="s">
         <v>1236</v>
       </c>
@@ -14362,7 +14362,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="311" spans="1:6">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A311" s="1" t="s">
         <v>1240</v>
       </c>
@@ -14382,7 +14382,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="312" spans="1:6">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A312" s="1" t="s">
         <v>1244</v>
       </c>
@@ -14402,7 +14402,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="313" spans="1:6">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A313" s="1" t="s">
         <v>1248</v>
       </c>
@@ -14422,7 +14422,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="314" spans="1:6">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A314" s="1" t="s">
         <v>1252</v>
       </c>
@@ -14442,7 +14442,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="315" spans="1:6">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A315" s="1" t="s">
         <v>1256</v>
       </c>
@@ -14462,7 +14462,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="316" spans="1:6">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A316" s="1" t="s">
         <v>1260</v>
       </c>
@@ -14482,7 +14482,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="317" spans="1:6">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A317" s="1" t="s">
         <v>1264</v>
       </c>
@@ -14502,7 +14502,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="318" spans="1:6">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A318" s="1" t="s">
         <v>1268</v>
       </c>
@@ -14522,7 +14522,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="319" spans="1:6">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A319" s="1" t="s">
         <v>1272</v>
       </c>
@@ -14542,7 +14542,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="320" spans="1:6">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A320" s="1" t="s">
         <v>1276</v>
       </c>
@@ -14562,7 +14562,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="321" spans="1:6">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A321" s="1" t="s">
         <v>1280</v>
       </c>
@@ -14582,7 +14582,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="322" spans="1:6">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A322" s="1" t="s">
         <v>1284</v>
       </c>
@@ -14602,7 +14602,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="323" spans="1:6">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A323" s="1" t="s">
         <v>1288</v>
       </c>
@@ -14622,7 +14622,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="324" spans="1:6">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A324" s="1" t="s">
         <v>1292</v>
       </c>
@@ -14642,7 +14642,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="325" spans="1:6">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A325" s="1" t="s">
         <v>1296</v>
       </c>
@@ -14662,7 +14662,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="326" spans="1:6">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A326" s="1" t="s">
         <v>1300</v>
       </c>
@@ -14682,7 +14682,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="327" spans="1:6">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A327" s="1" t="s">
         <v>1304</v>
       </c>
@@ -14702,7 +14702,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="328" spans="1:6">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A328" s="1" t="s">
         <v>1308</v>
       </c>
@@ -14722,7 +14722,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="329" spans="1:6">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A329" s="1" t="s">
         <v>1312</v>
       </c>
@@ -14742,7 +14742,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="330" spans="1:6">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A330" s="1" t="s">
         <v>1316</v>
       </c>
@@ -14762,7 +14762,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="331" spans="1:6">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A331" s="1" t="s">
         <v>1320</v>
       </c>
@@ -14782,7 +14782,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="332" spans="1:6">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A332" s="1" t="s">
         <v>1324</v>
       </c>
@@ -14802,7 +14802,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="333" spans="1:6">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A333" s="1" t="s">
         <v>1328</v>
       </c>
@@ -14822,7 +14822,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="334" spans="1:6">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A334" s="1" t="s">
         <v>1332</v>
       </c>
@@ -14842,7 +14842,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="335" spans="1:6">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A335" s="1" t="s">
         <v>1336</v>
       </c>
@@ -14862,7 +14862,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="336" spans="1:6">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A336" s="1" t="s">
         <v>1340</v>
       </c>
@@ -14882,7 +14882,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="337" spans="1:6">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A337" s="1" t="s">
         <v>1344</v>
       </c>
@@ -14902,7 +14902,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="338" spans="1:6">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A338" s="1" t="s">
         <v>1348</v>
       </c>
@@ -14922,7 +14922,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="339" spans="1:6">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A339" s="1" t="s">
         <v>1352</v>
       </c>
@@ -14942,7 +14942,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="340" spans="1:6">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A340" s="1" t="s">
         <v>1356</v>
       </c>
@@ -14962,7 +14962,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="341" spans="1:6">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A341" s="1" t="s">
         <v>1360</v>
       </c>
@@ -14982,7 +14982,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="342" spans="1:6">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A342" s="1" t="s">
         <v>1364</v>
       </c>
@@ -15002,7 +15002,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="343" spans="1:6">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A343" s="1" t="s">
         <v>1368</v>
       </c>
@@ -15022,7 +15022,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="344" spans="1:6">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A344" s="1" t="s">
         <v>1372</v>
       </c>
@@ -15042,7 +15042,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="345" spans="1:6">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A345" s="1" t="s">
         <v>1376</v>
       </c>
@@ -15062,7 +15062,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="346" spans="1:6">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A346" s="1" t="s">
         <v>1380</v>
       </c>
@@ -15082,7 +15082,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="347" spans="1:6">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A347" s="1" t="s">
         <v>1384</v>
       </c>
@@ -15102,7 +15102,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="348" spans="1:6">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A348" s="1" t="s">
         <v>1388</v>
       </c>
@@ -15122,7 +15122,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="349" spans="1:6">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A349" s="1" t="s">
         <v>1392</v>
       </c>
@@ -15142,7 +15142,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="350" spans="1:6">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A350" s="1" t="s">
         <v>1396</v>
       </c>
@@ -15162,7 +15162,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="351" spans="1:6">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A351" s="1" t="s">
         <v>1400</v>
       </c>
@@ -15182,7 +15182,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="352" spans="1:6">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A352" s="1" t="s">
         <v>1404</v>
       </c>
@@ -15202,7 +15202,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="353" spans="1:6">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A353" s="1" t="s">
         <v>1408</v>
       </c>
@@ -15222,7 +15222,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="354" spans="1:6">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A354" s="1" t="s">
         <v>1412</v>
       </c>
@@ -15242,7 +15242,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="355" spans="1:6">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
         <v>1416</v>
       </c>
@@ -15262,7 +15262,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="356" spans="1:6">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A356" s="1" t="s">
         <v>1420</v>
       </c>
@@ -15282,7 +15282,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="357" spans="1:6">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
         <v>1424</v>
       </c>
@@ -15302,7 +15302,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="358" spans="1:6">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A358" s="1" t="s">
         <v>1428</v>
       </c>
@@ -15322,7 +15322,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="359" spans="1:6">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
         <v>1432</v>
       </c>
@@ -15342,7 +15342,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="360" spans="1:6">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
         <v>1436</v>
       </c>
@@ -15362,7 +15362,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="361" spans="1:6">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
         <v>1440</v>
       </c>
@@ -15382,7 +15382,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="362" spans="1:6">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A362" s="1" t="s">
         <v>1444</v>
       </c>
@@ -15402,7 +15402,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="363" spans="1:6">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
         <v>1448</v>
       </c>
@@ -15422,7 +15422,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="364" spans="1:6">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
         <v>1452</v>
       </c>
@@ -15442,7 +15442,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="365" spans="1:6">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
         <v>1456</v>
       </c>
@@ -15462,7 +15462,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="366" spans="1:6">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
         <v>1460</v>
       </c>
@@ -15482,7 +15482,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="367" spans="1:6">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
         <v>1464</v>
       </c>
@@ -15502,7 +15502,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="368" spans="1:6">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
         <v>1468</v>
       </c>
@@ -15522,7 +15522,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="369" spans="1:6">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
         <v>1472</v>
       </c>
@@ -15542,7 +15542,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="370" spans="1:6">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
         <v>1476</v>
       </c>
@@ -15562,7 +15562,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="371" spans="1:6">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
         <v>1480</v>
       </c>
@@ -15582,7 +15582,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="372" spans="1:6">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
         <v>1484</v>
       </c>
@@ -15602,7 +15602,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="373" spans="1:6">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
         <v>1488</v>
       </c>
@@ -15622,7 +15622,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="374" spans="1:6">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
         <v>1492</v>
       </c>
@@ -15642,7 +15642,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="375" spans="1:6">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A375" s="1" t="s">
         <v>1496</v>
       </c>
@@ -15662,7 +15662,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="376" spans="1:6">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A376" s="1" t="s">
         <v>1500</v>
       </c>
@@ -15682,7 +15682,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="377" spans="1:6">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A377" s="1" t="s">
         <v>1504</v>
       </c>
@@ -15702,7 +15702,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="378" spans="1:6">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A378" s="1" t="s">
         <v>1508</v>
       </c>
@@ -15722,7 +15722,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="379" spans="1:6">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A379" s="1" t="s">
         <v>1512</v>
       </c>
@@ -15742,7 +15742,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="380" spans="1:6">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A380" s="1" t="s">
         <v>1516</v>
       </c>
@@ -15762,7 +15762,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="381" spans="1:6">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A381" s="1" t="s">
         <v>1520</v>
       </c>
@@ -15782,7 +15782,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="382" spans="1:6">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A382" s="1" t="s">
         <v>1524</v>
       </c>
@@ -15802,7 +15802,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="383" spans="1:6">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A383" s="1" t="s">
         <v>1528</v>
       </c>
@@ -15822,7 +15822,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="384" spans="1:6">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A384" s="1" t="s">
         <v>1532</v>
       </c>
@@ -15842,7 +15842,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="385" spans="1:6">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A385" s="1" t="s">
         <v>1536</v>
       </c>
@@ -15862,7 +15862,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="386" spans="1:6">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A386" s="1" t="s">
         <v>1540</v>
       </c>
@@ -15882,7 +15882,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="387" spans="1:6">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A387" s="1" t="s">
         <v>1544</v>
       </c>
@@ -15902,7 +15902,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="388" spans="1:6">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A388" s="1" t="s">
         <v>1548</v>
       </c>
@@ -15922,7 +15922,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="389" spans="1:6">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A389" s="1" t="s">
         <v>1552</v>
       </c>
@@ -15942,7 +15942,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="390" spans="1:6">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A390" s="1" t="s">
         <v>1556</v>
       </c>
@@ -15962,7 +15962,7 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="391" spans="1:6">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A391" s="1" t="s">
         <v>1560</v>
       </c>
@@ -15982,7 +15982,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="392" spans="1:6">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A392" s="1" t="s">
         <v>1564</v>
       </c>
@@ -16002,7 +16002,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="393" spans="1:6">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A393" s="1" t="s">
         <v>1568</v>
       </c>
@@ -16022,7 +16022,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="394" spans="1:6">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A394" s="1" t="s">
         <v>1572</v>
       </c>
@@ -16042,7 +16042,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="395" spans="1:6">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A395" s="1" t="s">
         <v>1576</v>
       </c>
@@ -16062,7 +16062,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="396" spans="1:6">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A396" s="1" t="s">
         <v>1580</v>
       </c>
@@ -16082,7 +16082,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="397" spans="1:6">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A397" s="1" t="s">
         <v>1584</v>
       </c>
@@ -16102,7 +16102,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="398" spans="1:6">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A398" s="1" t="s">
         <v>1588</v>
       </c>
@@ -16122,7 +16122,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="399" spans="1:6">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A399" s="1" t="s">
         <v>1592</v>
       </c>
@@ -16142,7 +16142,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="400" spans="1:6">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A400" s="1" t="s">
         <v>1596</v>
       </c>
@@ -16162,7 +16162,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="401" spans="1:6">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A401" s="1" t="s">
         <v>1600</v>
       </c>
@@ -16182,7 +16182,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="402" spans="1:6">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A402" s="1" t="s">
         <v>1604</v>
       </c>
@@ -16202,7 +16202,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="403" spans="1:6">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A403" s="1" t="s">
         <v>1608</v>
       </c>
@@ -16222,7 +16222,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="404" spans="1:6">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A404" s="1" t="s">
         <v>1612</v>
       </c>
@@ -16242,7 +16242,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="405" spans="1:6">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A405" s="1" t="s">
         <v>1616</v>
       </c>
@@ -16262,7 +16262,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="406" spans="1:6">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A406" s="1" t="s">
         <v>1620</v>
       </c>
@@ -16282,7 +16282,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="407" spans="1:6">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A407" s="1" t="s">
         <v>1624</v>
       </c>
@@ -16302,7 +16302,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="408" spans="1:6">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A408" s="1" t="s">
         <v>1628</v>
       </c>
@@ -16322,7 +16322,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="409" spans="1:6">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A409" s="1" t="s">
         <v>1632</v>
       </c>
@@ -16342,7 +16342,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="410" spans="1:6">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A410" s="1" t="s">
         <v>1636</v>
       </c>
@@ -16362,7 +16362,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="411" spans="1:6">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A411" s="1" t="s">
         <v>1640</v>
       </c>
@@ -16382,7 +16382,7 @@
         <v>1643</v>
       </c>
     </row>
-    <row r="412" spans="1:6">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A412" s="1" t="s">
         <v>1644</v>
       </c>
@@ -16402,7 +16402,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="413" spans="1:6">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A413" s="1" t="s">
         <v>1648</v>
       </c>
@@ -16422,7 +16422,7 @@
         <v>1651</v>
       </c>
     </row>
-    <row r="414" spans="1:6">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A414" s="1" t="s">
         <v>1652</v>
       </c>
@@ -16442,7 +16442,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="415" spans="1:6">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A415" s="1" t="s">
         <v>1656</v>
       </c>
@@ -16462,7 +16462,7 @@
         <v>1659</v>
       </c>
     </row>
-    <row r="416" spans="1:6">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A416" s="1" t="s">
         <v>1660</v>
       </c>
@@ -16482,7 +16482,7 @@
         <v>1663</v>
       </c>
     </row>
-    <row r="417" spans="1:6">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A417" s="1" t="s">
         <v>1664</v>
       </c>
@@ -16502,7 +16502,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="418" spans="1:6">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A418" s="1" t="s">
         <v>1668</v>
       </c>
@@ -16522,7 +16522,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="419" spans="1:6">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A419" s="1" t="s">
         <v>1672</v>
       </c>
@@ -16542,7 +16542,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="420" spans="1:6">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A420" s="1" t="s">
         <v>1676</v>
       </c>
@@ -16562,7 +16562,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="421" spans="1:6">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A421" s="1" t="s">
         <v>1680</v>
       </c>
@@ -16582,7 +16582,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="422" spans="1:6">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A422" s="1" t="s">
         <v>1684</v>
       </c>
@@ -16602,7 +16602,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="423" spans="1:6">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A423" s="1" t="s">
         <v>1688</v>
       </c>
@@ -16622,7 +16622,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="424" spans="1:6">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A424" s="1" t="s">
         <v>1692</v>
       </c>
@@ -16642,7 +16642,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="425" spans="1:6">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A425" s="1" t="s">
         <v>1696</v>
       </c>
@@ -16662,7 +16662,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="426" spans="1:6">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A426" s="1" t="s">
         <v>1700</v>
       </c>
@@ -16682,7 +16682,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="427" spans="1:6">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A427" s="1" t="s">
         <v>1704</v>
       </c>
@@ -16702,7 +16702,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="428" spans="1:6">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A428" s="1" t="s">
         <v>1708</v>
       </c>
@@ -16722,7 +16722,7 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="429" spans="1:6">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A429" s="1" t="s">
         <v>1712</v>
       </c>
@@ -16742,7 +16742,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="430" spans="1:6">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A430" s="1" t="s">
         <v>1716</v>
       </c>
@@ -16762,7 +16762,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="431" spans="1:6">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A431" s="1" t="s">
         <v>1720</v>
       </c>
@@ -16782,7 +16782,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="432" spans="1:6">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A432" s="1" t="s">
         <v>1724</v>
       </c>
@@ -16802,7 +16802,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="433" spans="1:6">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A433" s="1" t="s">
         <v>1728</v>
       </c>
@@ -16822,7 +16822,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="434" spans="1:6">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A434" s="1" t="s">
         <v>1732</v>
       </c>
@@ -16842,7 +16842,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="435" spans="1:6">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A435" s="1" t="s">
         <v>1736</v>
       </c>
@@ -16862,7 +16862,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="436" spans="1:6">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A436" s="1" t="s">
         <v>1740</v>
       </c>
@@ -16882,7 +16882,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="437" spans="1:6">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A437" s="1" t="s">
         <v>1744</v>
       </c>
@@ -16902,7 +16902,7 @@
         <v>1747</v>
       </c>
     </row>
-    <row r="438" spans="1:6">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A438" s="1" t="s">
         <v>1748</v>
       </c>
@@ -16922,7 +16922,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="439" spans="1:6">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A439" s="1" t="s">
         <v>1752</v>
       </c>
@@ -16942,7 +16942,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="440" spans="1:6">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A440" s="1" t="s">
         <v>1756</v>
       </c>
@@ -16962,7 +16962,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="441" spans="1:6">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A441" s="1" t="s">
         <v>1760</v>
       </c>
@@ -16982,7 +16982,7 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="442" spans="1:6">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A442" s="1" t="s">
         <v>1764</v>
       </c>
@@ -17002,7 +17002,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="443" spans="1:6">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A443" s="1" t="s">
         <v>1768</v>
       </c>
@@ -17022,7 +17022,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="444" spans="1:6">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A444" s="1" t="s">
         <v>1772</v>
       </c>
@@ -17042,7 +17042,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="445" spans="1:6">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A445" s="1" t="s">
         <v>1776</v>
       </c>
@@ -17062,7 +17062,7 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="446" spans="1:6">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A446" s="1" t="s">
         <v>1780</v>
       </c>
@@ -17082,7 +17082,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="447" spans="1:6">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A447" s="1" t="s">
         <v>1784</v>
       </c>
@@ -17102,7 +17102,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="448" spans="1:6">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A448" s="1" t="s">
         <v>1788</v>
       </c>
@@ -17122,7 +17122,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="449" spans="1:6">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A449" s="1" t="s">
         <v>1792</v>
       </c>
@@ -17142,7 +17142,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="450" spans="1:6">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A450" s="1" t="s">
         <v>1796</v>
       </c>
@@ -17162,7 +17162,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="451" spans="1:6">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A451" s="1" t="s">
         <v>1800</v>
       </c>
@@ -17182,7 +17182,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="452" spans="1:6">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A452" s="1" t="s">
         <v>1804</v>
       </c>
@@ -17202,7 +17202,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="453" spans="1:6">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A453" s="1" t="s">
         <v>1808</v>
       </c>
@@ -17222,7 +17222,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="454" spans="1:6">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A454" s="1" t="s">
         <v>1812</v>
       </c>
@@ -17242,7 +17242,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="455" spans="1:6">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A455" s="1" t="s">
         <v>1816</v>
       </c>
@@ -17262,7 +17262,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="456" spans="1:6">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A456" s="1" t="s">
         <v>1820</v>
       </c>
@@ -17282,7 +17282,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="457" spans="1:6">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A457" s="1" t="s">
         <v>1824</v>
       </c>
@@ -17302,7 +17302,7 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="458" spans="1:6">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A458" s="1" t="s">
         <v>1828</v>
       </c>
@@ -17322,7 +17322,7 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="459" spans="1:6">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A459" s="1" t="s">
         <v>1832</v>
       </c>
@@ -17342,7 +17342,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="460" spans="1:6">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A460" s="1" t="s">
         <v>1836</v>
       </c>
@@ -17362,7 +17362,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="461" spans="1:6">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A461" s="1" t="s">
         <v>1840</v>
       </c>
@@ -17382,7 +17382,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="462" spans="1:6">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A462" s="1" t="s">
         <v>1844</v>
       </c>
@@ -17402,7 +17402,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="463" spans="1:6">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A463" s="1" t="s">
         <v>1848</v>
       </c>
@@ -17422,7 +17422,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="464" spans="1:6">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A464" s="1" t="s">
         <v>1852</v>
       </c>
@@ -17442,7 +17442,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="465" spans="1:6">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A465" s="1" t="s">
         <v>1856</v>
       </c>
@@ -17462,7 +17462,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="466" spans="1:6">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A466" s="1" t="s">
         <v>1860</v>
       </c>
@@ -17482,7 +17482,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="467" spans="1:6">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A467" s="1" t="s">
         <v>1864</v>
       </c>
@@ -17502,7 +17502,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="468" spans="1:6">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A468" s="1" t="s">
         <v>1868</v>
       </c>
@@ -17522,7 +17522,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="469" spans="1:6">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A469" s="1" t="s">
         <v>1872</v>
       </c>
@@ -17542,7 +17542,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="470" spans="1:6">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A470" s="1" t="s">
         <v>1876</v>
       </c>
@@ -17562,7 +17562,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="471" spans="1:6">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A471" s="1" t="s">
         <v>1880</v>
       </c>
@@ -17582,7 +17582,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="472" spans="1:6">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A472" s="1" t="s">
         <v>1884</v>
       </c>
@@ -17602,7 +17602,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="473" spans="1:6">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A473" s="1" t="s">
         <v>1888</v>
       </c>
@@ -17622,7 +17622,7 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="474" spans="1:6">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A474" s="1" t="s">
         <v>1892</v>
       </c>
@@ -17642,7 +17642,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="475" spans="1:6">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A475" s="1" t="s">
         <v>1896</v>
       </c>
@@ -17662,7 +17662,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="476" spans="1:6">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A476" s="1" t="s">
         <v>1900</v>
       </c>
@@ -17682,7 +17682,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="477" spans="1:6">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A477" s="1" t="s">
         <v>1904</v>
       </c>
@@ -17702,7 +17702,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="478" spans="1:6">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A478" s="1" t="s">
         <v>1908</v>
       </c>
@@ -17722,7 +17722,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="479" spans="1:6">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A479" s="1" t="s">
         <v>1912</v>
       </c>
@@ -17742,7 +17742,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="480" spans="1:6">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A480" s="1" t="s">
         <v>1916</v>
       </c>
@@ -17762,7 +17762,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="481" spans="1:6">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A481" s="1" t="s">
         <v>1920</v>
       </c>
@@ -17782,7 +17782,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="482" spans="1:6">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A482" s="1" t="s">
         <v>1924</v>
       </c>
@@ -17802,7 +17802,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="483" spans="1:6">
+    <row r="483" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A483" s="1" t="s">
         <v>1928</v>
       </c>
@@ -17822,7 +17822,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="484" spans="1:6">
+    <row r="484" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A484" s="1" t="s">
         <v>1932</v>
       </c>
@@ -17842,7 +17842,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="485" spans="1:6">
+    <row r="485" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A485" s="1" t="s">
         <v>1936</v>
       </c>
@@ -17862,7 +17862,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="486" spans="1:6">
+    <row r="486" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A486" s="1" t="s">
         <v>1940</v>
       </c>
@@ -17882,7 +17882,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="487" spans="1:6">
+    <row r="487" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A487" s="1" t="s">
         <v>1944</v>
       </c>
@@ -17902,7 +17902,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="488" spans="1:6">
+    <row r="488" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A488" s="1" t="s">
         <v>1948</v>
       </c>
@@ -17922,7 +17922,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="489" spans="1:6">
+    <row r="489" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A489" s="1" t="s">
         <v>1952</v>
       </c>
@@ -17942,7 +17942,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="490" spans="1:6">
+    <row r="490" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A490" s="1" t="s">
         <v>1956</v>
       </c>
@@ -17962,7 +17962,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="491" spans="1:6">
+    <row r="491" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A491" s="1" t="s">
         <v>1960</v>
       </c>
@@ -17982,7 +17982,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="492" spans="1:6">
+    <row r="492" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A492" s="1" t="s">
         <v>1964</v>
       </c>
@@ -18002,7 +18002,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="493" spans="1:6">
+    <row r="493" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A493" s="1" t="s">
         <v>1968</v>
       </c>
@@ -18022,7 +18022,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="494" spans="1:6">
+    <row r="494" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A494" s="1" t="s">
         <v>1972</v>
       </c>
@@ -18042,7 +18042,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="495" spans="1:6">
+    <row r="495" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A495" s="1" t="s">
         <v>1976</v>
       </c>
@@ -18062,7 +18062,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="496" spans="1:6">
+    <row r="496" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A496" s="1" t="s">
         <v>1980</v>
       </c>
@@ -18082,7 +18082,7 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="497" spans="1:6">
+    <row r="497" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A497" s="1" t="s">
         <v>1984</v>
       </c>
@@ -18102,7 +18102,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="498" spans="1:6">
+    <row r="498" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A498" s="1" t="s">
         <v>1988</v>
       </c>
@@ -18122,7 +18122,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="499" spans="1:6">
+    <row r="499" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A499" s="1" t="s">
         <v>1992</v>
       </c>
@@ -18142,7 +18142,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="500" spans="1:6">
+    <row r="500" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A500" s="1" t="s">
         <v>1996</v>
       </c>
@@ -18162,7 +18162,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="501" spans="1:6">
+    <row r="501" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A501" s="1" t="s">
         <v>2000</v>
       </c>
@@ -18182,7 +18182,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="502" spans="1:6">
+    <row r="502" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A502" s="1" t="s">
         <v>2004</v>
       </c>
@@ -18202,7 +18202,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="503" spans="1:6">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A503" s="1" t="s">
         <v>2008</v>
       </c>
@@ -18222,7 +18222,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="504" spans="1:6">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A504" s="1" t="s">
         <v>2012</v>
       </c>
@@ -18242,7 +18242,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="505" spans="1:6">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A505" s="1" t="s">
         <v>2016</v>
       </c>
@@ -18262,7 +18262,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="506" spans="1:6">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A506" s="1" t="s">
         <v>2020</v>
       </c>
@@ -18282,7 +18282,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="507" spans="1:6">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A507" s="1" t="s">
         <v>2024</v>
       </c>
@@ -18302,7 +18302,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="508" spans="1:6">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A508" s="1" t="s">
         <v>2028</v>
       </c>
@@ -18322,7 +18322,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="509" spans="1:6">
+    <row r="509" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A509" s="1" t="s">
         <v>2032</v>
       </c>
@@ -18342,7 +18342,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="510" spans="1:6">
+    <row r="510" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A510" s="1" t="s">
         <v>2036</v>
       </c>
@@ -18362,7 +18362,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="511" spans="1:6">
+    <row r="511" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A511" s="1" t="s">
         <v>2040</v>
       </c>
@@ -18382,7 +18382,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="512" spans="1:6">
+    <row r="512" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A512" s="1" t="s">
         <v>2044</v>
       </c>
@@ -18402,7 +18402,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="513" spans="1:6">
+    <row r="513" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A513" s="1" t="s">
         <v>2048</v>
       </c>
@@ -18422,7 +18422,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="514" spans="1:6">
+    <row r="514" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A514" s="1" t="s">
         <v>2052</v>
       </c>
@@ -18442,7 +18442,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="515" spans="1:6">
+    <row r="515" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A515" s="1" t="s">
         <v>2056</v>
       </c>
@@ -18462,7 +18462,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="516" spans="1:6">
+    <row r="516" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A516" s="1" t="s">
         <v>2060</v>
       </c>
@@ -18482,7 +18482,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="517" spans="1:6">
+    <row r="517" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A517" s="1" t="s">
         <v>2064</v>
       </c>
@@ -18502,7 +18502,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="518" spans="1:6">
+    <row r="518" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A518" s="1" t="s">
         <v>2068</v>
       </c>
@@ -18522,7 +18522,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="519" spans="1:6">
+    <row r="519" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A519" s="1" t="s">
         <v>2072</v>
       </c>
@@ -18542,7 +18542,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="520" spans="1:6">
+    <row r="520" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A520" s="1" t="s">
         <v>2076</v>
       </c>
@@ -18562,7 +18562,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="521" spans="1:6">
+    <row r="521" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A521" s="1" t="s">
         <v>2080</v>
       </c>
@@ -18582,7 +18582,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="522" spans="1:6">
+    <row r="522" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A522" s="1" t="s">
         <v>2084</v>
       </c>
@@ -18602,7 +18602,7 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="523" spans="1:6">
+    <row r="523" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A523" s="1" t="s">
         <v>2088</v>
       </c>
@@ -18622,7 +18622,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="524" spans="1:6">
+    <row r="524" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A524" s="1" t="s">
         <v>2092</v>
       </c>
@@ -18642,7 +18642,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="525" spans="1:6">
+    <row r="525" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A525" s="1" t="s">
         <v>2096</v>
       </c>
@@ -18662,7 +18662,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="526" spans="1:6">
+    <row r="526" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A526" s="1" t="s">
         <v>2100</v>
       </c>
@@ -18682,7 +18682,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="527" spans="1:6">
+    <row r="527" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A527" s="1" t="s">
         <v>2104</v>
       </c>
@@ -18702,7 +18702,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="528" spans="1:6">
+    <row r="528" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A528" s="1" t="s">
         <v>2108</v>
       </c>
@@ -18722,7 +18722,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="529" spans="1:6">
+    <row r="529" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A529" s="1" t="s">
         <v>2112</v>
       </c>
@@ -18742,7 +18742,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="530" spans="1:6">
+    <row r="530" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A530" s="1" t="s">
         <v>2116</v>
       </c>
@@ -18762,7 +18762,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="531" spans="1:6">
+    <row r="531" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A531" s="1" t="s">
         <v>2120</v>
       </c>
@@ -18782,7 +18782,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="532" spans="1:6">
+    <row r="532" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A532" s="1" t="s">
         <v>2124</v>
       </c>
@@ -18802,7 +18802,7 @@
         <v>2127</v>
       </c>
     </row>
-    <row r="533" spans="1:6">
+    <row r="533" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A533" s="1" t="s">
         <v>2128</v>
       </c>
@@ -18822,7 +18822,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="534" spans="1:6">
+    <row r="534" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A534" s="1" t="s">
         <v>2132</v>
       </c>
@@ -18842,7 +18842,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="535" spans="1:6">
+    <row r="535" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A535" s="1" t="s">
         <v>2136</v>
       </c>
@@ -18862,7 +18862,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="536" spans="1:6">
+    <row r="536" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A536" s="1" t="s">
         <v>2140</v>
       </c>
@@ -18882,7 +18882,7 @@
         <v>2143</v>
       </c>
     </row>
-    <row r="537" spans="1:6">
+    <row r="537" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A537" s="1" t="s">
         <v>2144</v>
       </c>
@@ -18902,7 +18902,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="538" spans="1:6">
+    <row r="538" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A538" s="1" t="s">
         <v>2148</v>
       </c>
@@ -18922,7 +18922,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="539" spans="1:6">
+    <row r="539" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A539" s="1" t="s">
         <v>2152</v>
       </c>
@@ -18942,7 +18942,7 @@
         <v>2155</v>
       </c>
     </row>
-    <row r="540" spans="1:6">
+    <row r="540" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A540" s="1" t="s">
         <v>2156</v>
       </c>
@@ -18962,7 +18962,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="541" spans="1:6">
+    <row r="541" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A541" s="1" t="s">
         <v>2160</v>
       </c>
@@ -18982,7 +18982,7 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="542" spans="1:6">
+    <row r="542" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A542" s="1" t="s">
         <v>2164</v>
       </c>
@@ -19002,7 +19002,7 @@
         <v>2167</v>
       </c>
     </row>
-    <row r="543" spans="1:6">
+    <row r="543" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A543" s="1" t="s">
         <v>2168</v>
       </c>
@@ -19022,7 +19022,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="544" spans="1:6">
+    <row r="544" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A544" s="1" t="s">
         <v>2172</v>
       </c>
@@ -19042,7 +19042,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="545" spans="1:6">
+    <row r="545" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A545" s="1" t="s">
         <v>2176</v>
       </c>
@@ -19062,7 +19062,7 @@
         <v>2179</v>
       </c>
     </row>
-    <row r="546" spans="1:6">
+    <row r="546" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A546" s="1" t="s">
         <v>2180</v>
       </c>
@@ -19082,7 +19082,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="547" spans="1:6">
+    <row r="547" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A547" s="1" t="s">
         <v>2184</v>
       </c>
@@ -19102,7 +19102,7 @@
         <v>2187</v>
       </c>
     </row>
-    <row r="548" spans="1:6">
+    <row r="548" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A548" s="1" t="s">
         <v>2188</v>
       </c>
@@ -19122,7 +19122,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="549" spans="1:6">
+    <row r="549" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A549" s="1" t="s">
         <v>2192</v>
       </c>
@@ -19142,7 +19142,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="550" spans="1:6">
+    <row r="550" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A550" s="1" t="s">
         <v>2196</v>
       </c>
@@ -19162,7 +19162,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="551" spans="1:6">
+    <row r="551" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A551" s="1" t="s">
         <v>2200</v>
       </c>
@@ -19182,7 +19182,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="552" spans="1:6">
+    <row r="552" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A552" s="1" t="s">
         <v>2204</v>
       </c>
@@ -19202,7 +19202,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="553" spans="1:6">
+    <row r="553" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A553" s="1" t="s">
         <v>2208</v>
       </c>
@@ -19222,7 +19222,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="554" spans="1:6">
+    <row r="554" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A554" s="1" t="s">
         <v>2212</v>
       </c>
@@ -19242,7 +19242,7 @@
         <v>2215</v>
       </c>
     </row>
-    <row r="555" spans="1:6">
+    <row r="555" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A555" s="1" t="s">
         <v>2216</v>
       </c>
@@ -19262,7 +19262,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="556" spans="1:6">
+    <row r="556" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A556" s="1" t="s">
         <v>2220</v>
       </c>
@@ -19282,7 +19282,7 @@
         <v>2223</v>
       </c>
     </row>
-    <row r="557" spans="1:6">
+    <row r="557" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A557" s="1" t="s">
         <v>2224</v>
       </c>
@@ -19302,7 +19302,7 @@
         <v>2227</v>
       </c>
     </row>
-    <row r="558" spans="1:6">
+    <row r="558" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A558" s="1" t="s">
         <v>2228</v>
       </c>
@@ -19322,7 +19322,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="559" spans="1:6">
+    <row r="559" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A559" s="1" t="s">
         <v>2232</v>
       </c>
@@ -19342,7 +19342,7 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="560" spans="1:6">
+    <row r="560" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A560" s="1" t="s">
         <v>2236</v>
       </c>
@@ -19362,7 +19362,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="561" spans="1:6">
+    <row r="561" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A561" s="1" t="s">
         <v>2240</v>
       </c>
@@ -19382,7 +19382,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="562" spans="1:6">
+    <row r="562" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A562" s="1" t="s">
         <v>2244</v>
       </c>
@@ -19402,7 +19402,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="563" spans="1:6">
+    <row r="563" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A563" s="1" t="s">
         <v>2248</v>
       </c>
@@ -19422,7 +19422,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="564" spans="1:6">
+    <row r="564" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A564" s="1" t="s">
         <v>2252</v>
       </c>
@@ -19442,7 +19442,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="565" spans="1:6">
+    <row r="565" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A565" s="1" t="s">
         <v>2256</v>
       </c>
@@ -19462,7 +19462,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="566" spans="1:6">
+    <row r="566" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A566" s="1" t="s">
         <v>2260</v>
       </c>
@@ -19482,7 +19482,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="567" spans="1:6">
+    <row r="567" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A567" s="1" t="s">
         <v>2264</v>
       </c>
@@ -19502,7 +19502,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="568" spans="1:6">
+    <row r="568" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A568" s="1" t="s">
         <v>2268</v>
       </c>
@@ -19522,7 +19522,7 @@
         <v>2271</v>
       </c>
     </row>
-    <row r="569" spans="1:6">
+    <row r="569" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A569" s="1" t="s">
         <v>2272</v>
       </c>
@@ -19542,7 +19542,7 @@
         <v>2275</v>
       </c>
     </row>
-    <row r="570" spans="1:6">
+    <row r="570" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A570" s="1" t="s">
         <v>2276</v>
       </c>
@@ -19562,7 +19562,7 @@
         <v>2279</v>
       </c>
     </row>
-    <row r="571" spans="1:6">
+    <row r="571" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A571" s="1" t="s">
         <v>2280</v>
       </c>
@@ -19582,7 +19582,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="572" spans="1:6">
+    <row r="572" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A572" s="1" t="s">
         <v>2284</v>
       </c>
@@ -19602,7 +19602,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="573" spans="1:6">
+    <row r="573" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A573" s="1" t="s">
         <v>2288</v>
       </c>
@@ -19622,7 +19622,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="574" spans="1:6">
+    <row r="574" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A574" s="1" t="s">
         <v>2292</v>
       </c>
@@ -19642,7 +19642,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="575" spans="1:6">
+    <row r="575" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A575" s="1" t="s">
         <v>2296</v>
       </c>
@@ -19662,7 +19662,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="576" spans="1:6">
+    <row r="576" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A576" s="1" t="s">
         <v>2300</v>
       </c>
@@ -19682,7 +19682,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="577" spans="1:6">
+    <row r="577" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A577" s="1" t="s">
         <v>2304</v>
       </c>
@@ -19702,7 +19702,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="578" spans="1:6">
+    <row r="578" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A578" s="1" t="s">
         <v>2308</v>
       </c>
@@ -19722,7 +19722,7 @@
         <v>2311</v>
       </c>
     </row>
-    <row r="579" spans="1:6">
+    <row r="579" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A579" s="1" t="s">
         <v>2312</v>
       </c>
@@ -19742,7 +19742,7 @@
         <v>2315</v>
       </c>
     </row>
-    <row r="580" spans="1:6">
+    <row r="580" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A580" s="1" t="s">
         <v>2316</v>
       </c>
@@ -19762,7 +19762,7 @@
         <v>2319</v>
       </c>
     </row>
-    <row r="581" spans="1:6">
+    <row r="581" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A581" s="1" t="s">
         <v>2320</v>
       </c>
@@ -19782,7 +19782,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="582" spans="1:6">
+    <row r="582" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A582" s="1" t="s">
         <v>2324</v>
       </c>
@@ -19802,7 +19802,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="583" spans="1:6">
+    <row r="583" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A583" s="1" t="s">
         <v>2328</v>
       </c>
@@ -19822,7 +19822,7 @@
         <v>2331</v>
       </c>
     </row>
-    <row r="584" spans="1:6">
+    <row r="584" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A584" s="1" t="s">
         <v>2332</v>
       </c>
@@ -19842,7 +19842,7 @@
         <v>2335</v>
       </c>
     </row>
-    <row r="585" spans="1:6">
+    <row r="585" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A585" s="1" t="s">
         <v>2336</v>
       </c>
@@ -19862,7 +19862,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="586" spans="1:6">
+    <row r="586" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A586" s="1" t="s">
         <v>2340</v>
       </c>
@@ -19882,7 +19882,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="587" spans="1:6">
+    <row r="587" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A587" s="1" t="s">
         <v>2344</v>
       </c>
@@ -19902,7 +19902,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="588" spans="1:6">
+    <row r="588" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A588" s="1" t="s">
         <v>2348</v>
       </c>
@@ -19922,7 +19922,7 @@
         <v>2351</v>
       </c>
     </row>
-    <row r="589" spans="1:6">
+    <row r="589" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A589" s="1" t="s">
         <v>2352</v>
       </c>
@@ -19942,7 +19942,7 @@
         <v>2355</v>
       </c>
     </row>
-    <row r="590" spans="1:6">
+    <row r="590" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A590" s="1" t="s">
         <v>2356</v>
       </c>
@@ -19962,7 +19962,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="591" spans="1:6">
+    <row r="591" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A591" s="1" t="s">
         <v>2360</v>
       </c>
@@ -19982,7 +19982,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="592" spans="1:6">
+    <row r="592" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A592" s="1" t="s">
         <v>2364</v>
       </c>
@@ -20002,7 +20002,7 @@
         <v>2367</v>
       </c>
     </row>
-    <row r="593" spans="1:6">
+    <row r="593" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A593" s="1" t="s">
         <v>2368</v>
       </c>
@@ -20022,7 +20022,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="594" spans="1:6">
+    <row r="594" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A594" s="1" t="s">
         <v>2372</v>
       </c>
@@ -20042,7 +20042,7 @@
         <v>2375</v>
       </c>
     </row>
-    <row r="595" spans="1:6">
+    <row r="595" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A595" s="1" t="s">
         <v>2376</v>
       </c>
@@ -20062,7 +20062,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="596" spans="1:6">
+    <row r="596" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A596" s="1" t="s">
         <v>2380</v>
       </c>
@@ -20082,7 +20082,7 @@
         <v>2383</v>
       </c>
     </row>
-    <row r="597" spans="1:6">
+    <row r="597" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A597" s="1" t="s">
         <v>2384</v>
       </c>
@@ -20102,7 +20102,7 @@
         <v>2387</v>
       </c>
     </row>
-    <row r="598" spans="1:6">
+    <row r="598" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A598" s="1" t="s">
         <v>2388</v>
       </c>
@@ -20122,7 +20122,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="599" spans="1:6">
+    <row r="599" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A599" s="1" t="s">
         <v>2392</v>
       </c>
@@ -20142,7 +20142,7 @@
         <v>2395</v>
       </c>
     </row>
-    <row r="600" spans="1:6">
+    <row r="600" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A600" s="1" t="s">
         <v>2396</v>
       </c>
@@ -20162,7 +20162,7 @@
         <v>2399</v>
       </c>
     </row>
-    <row r="601" spans="1:6">
+    <row r="601" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A601" s="1" t="s">
         <v>2400</v>
       </c>
@@ -20182,7 +20182,7 @@
         <v>2403</v>
       </c>
     </row>
-    <row r="602" spans="1:6">
+    <row r="602" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A602" s="1" t="s">
         <v>2404</v>
       </c>
@@ -20202,7 +20202,7 @@
         <v>2407</v>
       </c>
     </row>
-    <row r="603" spans="1:6">
+    <row r="603" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A603" s="1" t="s">
         <v>2408</v>
       </c>
@@ -20222,7 +20222,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="604" spans="1:6">
+    <row r="604" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A604" s="1" t="s">
         <v>2412</v>
       </c>
@@ -20242,7 +20242,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="605" spans="1:6">
+    <row r="605" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A605" s="1" t="s">
         <v>2416</v>
       </c>
@@ -20262,7 +20262,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="606" spans="1:6">
+    <row r="606" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A606" s="1" t="s">
         <v>2420</v>
       </c>
@@ -20282,7 +20282,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="607" spans="1:6">
+    <row r="607" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A607" s="1" t="s">
         <v>2424</v>
       </c>
@@ -20302,7 +20302,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="608" spans="1:6">
+    <row r="608" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A608" s="1" t="s">
         <v>2428</v>
       </c>
@@ -20322,7 +20322,7 @@
         <v>2431</v>
       </c>
     </row>
-    <row r="609" spans="1:6">
+    <row r="609" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A609" s="1" t="s">
         <v>2432</v>
       </c>
@@ -20342,7 +20342,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="610" spans="1:6">
+    <row r="610" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A610" s="1" t="s">
         <v>2436</v>
       </c>
@@ -20362,7 +20362,7 @@
         <v>2439</v>
       </c>
     </row>
-    <row r="611" spans="1:6">
+    <row r="611" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A611" s="1" t="s">
         <v>2440</v>
       </c>
@@ -20382,7 +20382,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="612" spans="1:6">
+    <row r="612" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A612" s="1" t="s">
         <v>2444</v>
       </c>
@@ -20402,7 +20402,7 @@
         <v>2447</v>
       </c>
     </row>
-    <row r="613" spans="1:6">
+    <row r="613" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A613" s="1" t="s">
         <v>2448</v>
       </c>
@@ -20422,7 +20422,7 @@
         <v>2451</v>
       </c>
     </row>
-    <row r="614" spans="1:6">
+    <row r="614" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A614" s="1" t="s">
         <v>2452</v>
       </c>
@@ -20442,7 +20442,7 @@
         <v>2455</v>
       </c>
     </row>
-    <row r="615" spans="1:6">
+    <row r="615" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A615" s="1" t="s">
         <v>2456</v>
       </c>
@@ -20462,7 +20462,7 @@
         <v>2459</v>
       </c>
     </row>
-    <row r="616" spans="1:6">
+    <row r="616" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A616" s="1" t="s">
         <v>2460</v>
       </c>
@@ -20482,7 +20482,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="617" spans="1:6">
+    <row r="617" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A617" s="1" t="s">
         <v>2464</v>
       </c>
@@ -20502,7 +20502,7 @@
         <v>2467</v>
       </c>
     </row>
-    <row r="618" spans="1:6">
+    <row r="618" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A618" s="1" t="s">
         <v>2468</v>
       </c>
@@ -20522,7 +20522,7 @@
         <v>2471</v>
       </c>
     </row>
-    <row r="619" spans="1:6">
+    <row r="619" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A619" s="1" t="s">
         <v>2472</v>
       </c>
@@ -20542,7 +20542,7 @@
         <v>2474</v>
       </c>
     </row>
-    <row r="620" spans="1:6">
+    <row r="620" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A620" s="1" t="s">
         <v>2475</v>
       </c>
@@ -20562,7 +20562,7 @@
         <v>2477</v>
       </c>
     </row>
-    <row r="621" spans="1:6">
+    <row r="621" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A621" s="1" t="s">
         <v>2478</v>
       </c>
@@ -20582,7 +20582,7 @@
         <v>2480</v>
       </c>
     </row>
-    <row r="622" spans="1:6">
+    <row r="622" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A622" s="1" t="s">
         <v>2481</v>
       </c>
@@ -20602,7 +20602,7 @@
         <v>2483</v>
       </c>
     </row>
-    <row r="623" spans="1:6">
+    <row r="623" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A623" s="1" t="s">
         <v>2484</v>
       </c>
@@ -20622,7 +20622,7 @@
         <v>2486</v>
       </c>
     </row>
-    <row r="624" spans="1:6">
+    <row r="624" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A624" s="1" t="s">
         <v>2487</v>
       </c>
@@ -20642,7 +20642,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="625" spans="1:6">
+    <row r="625" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A625" s="1" t="s">
         <v>2490</v>
       </c>
@@ -20662,7 +20662,7 @@
         <v>2492</v>
       </c>
     </row>
-    <row r="626" spans="1:6">
+    <row r="626" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A626" s="1" t="s">
         <v>2493</v>
       </c>
@@ -20682,7 +20682,7 @@
         <v>2495</v>
       </c>
     </row>
-    <row r="627" spans="1:6">
+    <row r="627" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A627" s="1" t="s">
         <v>2496</v>
       </c>
@@ -20711,16 +20711,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7E28C7A-5F7C-4CD4-8D6D-284795F459CA}">
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="51.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="51.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>2499</v>
       </c>
@@ -20736,7 +20736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2501</v>
       </c>
@@ -20758,7 +20758,7 @@
         <v>/app/nrt/R63_NRTLIVE/NRT/SH</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2505</v>
       </c>
@@ -20780,7 +20780,7 @@
         <v>/app/nrt/R63_NRTLIVE/NRT/CFG</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>2507</v>
       </c>
@@ -20802,7 +20802,7 @@
         <v>/app/nrt/R63_NRTLIVE/NRT/EXE</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>2509</v>
       </c>
@@ -20824,7 +20824,7 @@
         <v>/app/nrt/R63_NRTLIVE/NRT/SQL</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -20835,7 +20835,7 @@
         <v>/R63_NRTLIVE</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>2511</v>
       </c>
@@ -20857,7 +20857,7 @@
         <v>/data/nrt/R63_NRTLIVE/NRT/LOG</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>2514</v>
       </c>
@@ -20879,7 +20879,7 @@
         <v>/data/nrt/R63_NRTLIVE/NRT/REPORTS</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>2516</v>
       </c>
@@ -20901,7 +20901,7 @@
         <v>/data/nrt/R63_NRTLIVE/NRT/IB_SDM/LATE_FILES</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>2519</v>
       </c>
@@ -20923,7 +20923,7 @@
         <v>/data/nrt/R63_NRTLIVE/NRT/IB_SDM/RECEIVED_FILES</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>2522</v>
       </c>
@@ -20945,7 +20945,7 @@
         <v>/data/nrt/R63_NRTLIVE/NRT/IB_SDM/REPORTS</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>2525</v>
       </c>
@@ -20967,7 +20967,7 @@
         <v>/data/nrt/R63_NRTLIVE/NRT/IB_SDM/SENT_FILES</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>2528</v>
       </c>
@@ -20989,7 +20989,7 @@
         <v>/data/nrt/R63_NRTLIVE/NRT/OB_MACH/ARCHIVE_FILES</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>2531</v>
       </c>
@@ -21011,7 +21011,7 @@
         <v>/data/nrt/R63_NRTLIVE/NRT/OB_MACH/AUDIT_FILES</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>2534</v>
       </c>
@@ -21033,7 +21033,7 @@
         <v>/data/nrt/R63_NRTLIVE/NRT/OB_MACH/ERROR_FILES</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>2537</v>
       </c>
@@ -21055,7 +21055,7 @@
         <v>/data/nrt/R63_NRTLIVE/NRT/OB_MACH/PROCESSED_FILES</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>2540</v>
       </c>
@@ -21077,7 +21077,7 @@
         <v>/data/nrt/R63_NRTLIVE/NRT/OB_MACH/RECEIVED_FILES</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>2543</v>
       </c>
@@ -21099,7 +21099,7 @@
         <v>/data/nrt/R63_NRTLIVE/NRT/OB_MACH/REPORTS</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>2546</v>
       </c>
@@ -21121,7 +21121,7 @@
         <v>/data/nrt/R63_NRTLIVE/NRT/OB_MACH/UNZIPPED_FILES</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>2549</v>
       </c>
@@ -21143,7 +21143,7 @@
         <v>/data/nrt/R63_NRTLIVE/NRT/OB_MACH/WIP_FILES</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>2552</v>
       </c>
@@ -21165,7 +21165,7 @@
         <v>/data/nrt/R63_NRTLIVE/NRT/OB_FMS/FILES_TO_FMSLIVE</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>2555</v>
       </c>
@@ -21187,7 +21187,7 @@
         <v>/data/nrt/R63_NRTLIVE/NRT/OB_FMS/FILES_TO_FMSDR</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>2558</v>
       </c>
@@ -21209,7 +21209,7 @@
         <v>/data/nrt/R63_NRTLIVE/NRT/OB_FMS/FILES_READY_TO_SEND</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
       <c r="B24" s="1" t="s">
         <v>2561</v>
@@ -21229,7 +21229,7 @@
         <v>chroot/R63_NRTLIVE/NRT_MFT/INCOMING</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
         <v>2563</v>
@@ -21249,7 +21249,7 @@
         <v>chroot/R63_NRTLIVE/NRT_MFT/OUTGOING</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1"/>
       <c r="B26" s="1" t="s">
         <v>2565</v>
@@ -21269,7 +21269,7 @@
         <v>chroot/R63_NRTLIVE/NRT_MFT/INCOMING/SDM</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
         <v>2567</v>
@@ -21289,7 +21289,7 @@
         <v>chroot/R63_NRTLIVE/NRT_MFT/INCOMING/MACH</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="1"/>
       <c r="B28" s="1" t="s">
         <v>2569</v>
@@ -21309,7 +21309,7 @@
         <v>chroot/R63_NRTLIVE/NRT_MFT/OUTGOING/MACH</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="1"/>
       <c r="B29" s="1" t="s">
         <v>2571</v>
@@ -21329,7 +21329,7 @@
         <v>chroot/R63_NRTLIVE/NRT_MFT/OUTGOING/FMSLIVE</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="1"/>
       <c r="B30" s="1" t="s">
         <v>2573</v>

--- a/TAP n NRT directories.xlsx
+++ b/TAP n NRT directories.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myoffice.accenture.com/personal/v_brabhaharan_accenture_com/Documents/Documents/VMO2/TAP/Script_Opus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{75BF60A8-BB22-4744-A2CE-ACD735186B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03656DF8-AD99-4364-AC52-876415F14205}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{75BF60A8-BB22-4744-A2CE-ACD735186B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50C1C518-784E-45B2-9146-3922206ECF0A}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4800" yWindow="3110" windowWidth="14400" windowHeight="8170" xr2:uid="{0E8EA9B8-1E59-4C3E-9E23-98E6D03B5A03}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0E8EA9B8-1E59-4C3E-9E23-98E6D03B5A03}"/>
   </bookViews>
   <sheets>
     <sheet name="TAP" sheetId="1" r:id="rId1"/>
@@ -8165,7 +8165,7 @@
   <dimension ref="A1:F627"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.81640625" customWidth="1"/>
     <col min="2" max="3" width="19.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40.453125" customWidth="1"/>
